--- a/data/trans_dic/P21D_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 3486</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2569</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3820</t>
+          <t>0; 3861</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3440</t>
+          <t>0; 3456</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1350</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1569</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2192</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4645</t>
+          <t>0; 4688</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_1_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_1_R-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,17</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3512</t>
+          <t>0; 4321</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3486</t>
+          <t>0; 3548</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3861</t>
+          <t>0; 3762</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3456</t>
+          <t>0; 3803</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 5154</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4688</t>
+          <t>0; 4546</t>
         </is>
       </c>
     </row>
